--- a/Deliverables/BOM/BOB_MCF8316/eSpark BOM.xlsx
+++ b/Deliverables/BOM/BOB_MCF8316/eSpark BOM.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="206">
   <si>
     <t>Component list</t>
   </si>
@@ -644,6 +644,12 @@
   </si>
   <si>
     <t>IC to find</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Component Cost </t>
+  </si>
+  <si>
+    <t>Single Board Cost</t>
   </si>
 </sst>
 </file>
@@ -654,7 +660,7 @@
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -820,6 +826,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -859,7 +880,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1104,12 +1125,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -1273,6 +1335,36 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1297,35 +1389,28 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="16" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="25" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1669,7 +1754,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S39"/>
+  <dimension ref="A1:S44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1703,15 +1788,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="61"/>
-      <c r="L1" s="61"/>
-      <c r="M1" s="61"/>
-      <c r="N1" s="61"/>
-      <c r="O1" s="61"/>
-      <c r="P1" s="61"/>
-      <c r="Q1" s="61"/>
-      <c r="R1" s="61"/>
-      <c r="S1" s="62"/>
+      <c r="K1" s="71"/>
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="71"/>
+      <c r="O1" s="71"/>
+      <c r="P1" s="71"/>
+      <c r="Q1" s="71"/>
+      <c r="R1" s="71"/>
+      <c r="S1" s="72"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1761,7 +1846,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="63"/>
+      <c r="S3" s="73"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1786,7 +1871,7 @@
       <c r="P4" s="7"/>
       <c r="Q4" s="7"/>
       <c r="R4" s="7"/>
-      <c r="S4" s="64"/>
+      <c r="S4" s="74"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1811,7 +1896,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="64"/>
+      <c r="S5" s="74"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1832,7 +1917,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="64"/>
+      <c r="S6" s="74"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1853,7 +1938,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="64"/>
+      <c r="S7" s="74"/>
     </row>
     <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1874,7 +1959,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="64"/>
+      <c r="S8" s="74"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1939,7 +2024,7 @@
         <f>ROW(B10) - ROW($B$9)</f>
         <v>1</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="62" t="s">
         <v>147</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -1974,7 +2059,7 @@
       <c r="N10" s="46">
         <v>20</v>
       </c>
-      <c r="O10" s="73" t="s">
+      <c r="O10" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P10" s="55">
@@ -1992,7 +2077,7 @@
         <f t="shared" ref="B11:B37" si="0">ROW(B11) - ROW($B$9)</f>
         <v>2</v>
       </c>
-      <c r="C11" s="71" t="s">
+      <c r="C11" s="63" t="s">
         <v>147</v>
       </c>
       <c r="D11" s="50" t="s">
@@ -2027,7 +2112,7 @@
       <c r="N11" s="50">
         <v>12</v>
       </c>
-      <c r="O11" s="74" t="s">
+      <c r="O11" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P11" s="56">
@@ -2045,7 +2130,7 @@
         <f>ROW(B12) - ROW($B$9)</f>
         <v>3</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="62" t="s">
         <v>147</v>
       </c>
       <c r="D12" s="46" t="s">
@@ -2080,7 +2165,7 @@
       <c r="N12" s="46">
         <v>25</v>
       </c>
-      <c r="O12" s="73" t="s">
+      <c r="O12" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P12" s="55">
@@ -2098,7 +2183,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="71" t="s">
+      <c r="C13" s="63" t="s">
         <v>147</v>
       </c>
       <c r="D13" s="50" t="s">
@@ -2133,7 +2218,7 @@
       <c r="N13" s="50">
         <v>100</v>
       </c>
-      <c r="O13" s="74" t="s">
+      <c r="O13" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P13" s="56">
@@ -2151,7 +2236,7 @@
         <f>ROW(B14) - ROW($B$9)</f>
         <v>5</v>
       </c>
-      <c r="C14" s="70" t="s">
+      <c r="C14" s="62" t="s">
         <v>147</v>
       </c>
       <c r="D14" s="46" t="s">
@@ -2186,7 +2271,7 @@
       <c r="N14" s="46">
         <v>50</v>
       </c>
-      <c r="O14" s="73" t="s">
+      <c r="O14" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P14" s="55">
@@ -2204,7 +2289,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="71" t="s">
+      <c r="C15" s="63" t="s">
         <v>147</v>
       </c>
       <c r="D15" s="50" t="s">
@@ -2239,7 +2324,7 @@
       <c r="N15" s="50">
         <v>100</v>
       </c>
-      <c r="O15" s="74" t="s">
+      <c r="O15" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P15" s="56">
@@ -2257,7 +2342,7 @@
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="70" t="s">
+      <c r="C16" s="62" t="s">
         <v>147</v>
       </c>
       <c r="D16" s="46" t="s">
@@ -2292,7 +2377,7 @@
       <c r="N16" s="46">
         <v>50</v>
       </c>
-      <c r="O16" s="73" t="s">
+      <c r="O16" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P16" s="55">
@@ -2310,7 +2395,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="71" t="s">
+      <c r="C17" s="63" t="s">
         <v>147</v>
       </c>
       <c r="D17" s="50" t="s">
@@ -2345,7 +2430,7 @@
       <c r="N17" s="50">
         <v>12</v>
       </c>
-      <c r="O17" s="74" t="s">
+      <c r="O17" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P17" s="56">
@@ -2363,7 +2448,7 @@
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="70" t="s">
+      <c r="C18" s="62" t="s">
         <v>147</v>
       </c>
       <c r="D18" s="46" t="s">
@@ -2375,7 +2460,7 @@
       <c r="F18" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="G18" s="75">
+      <c r="G18" s="67">
         <v>885012205080</v>
       </c>
       <c r="H18" s="46" t="s">
@@ -2400,7 +2485,7 @@
       <c r="N18" s="46">
         <v>100</v>
       </c>
-      <c r="O18" s="73" t="s">
+      <c r="O18" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P18" s="55">
@@ -2418,7 +2503,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="71" t="s">
+      <c r="C19" s="63" t="s">
         <v>148</v>
       </c>
       <c r="D19" s="50" t="s">
@@ -2453,7 +2538,7 @@
       <c r="N19" s="50">
         <v>20</v>
       </c>
-      <c r="O19" s="74" t="s">
+      <c r="O19" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P19" s="56">
@@ -2471,7 +2556,7 @@
         <f>ROW(B20) - ROW($B$9)</f>
         <v>11</v>
       </c>
-      <c r="C20" s="70" t="s">
+      <c r="C20" s="62" t="s">
         <v>149</v>
       </c>
       <c r="D20" s="46" t="s">
@@ -2506,7 +2591,7 @@
       <c r="N20" s="46">
         <v>15</v>
       </c>
-      <c r="O20" s="73" t="s">
+      <c r="O20" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P20" s="55">
@@ -2524,7 +2609,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="71" t="s">
+      <c r="C21" s="63" t="s">
         <v>149</v>
       </c>
       <c r="D21" s="50" t="s">
@@ -2559,7 +2644,7 @@
       <c r="N21" s="50">
         <v>50</v>
       </c>
-      <c r="O21" s="74" t="s">
+      <c r="O21" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P21" s="56">
@@ -2577,7 +2662,7 @@
         <f>ROW(B22) - ROW($B$9)</f>
         <v>13</v>
       </c>
-      <c r="C22" s="70" t="s">
+      <c r="C22" s="62" t="s">
         <v>149</v>
       </c>
       <c r="D22" s="46" t="s">
@@ -2612,7 +2697,7 @@
       <c r="N22" s="46">
         <v>15</v>
       </c>
-      <c r="O22" s="73" t="s">
+      <c r="O22" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P22" s="55">
@@ -2630,7 +2715,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="71" t="s">
+      <c r="C23" s="63" t="s">
         <v>150</v>
       </c>
       <c r="D23" s="50" t="s">
@@ -2665,7 +2750,7 @@
       <c r="N23" s="50">
         <v>20</v>
       </c>
-      <c r="O23" s="74" t="s">
+      <c r="O23" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P23" s="56">
@@ -2683,7 +2768,7 @@
         <f>ROW(B24) - ROW($B$9)</f>
         <v>15</v>
       </c>
-      <c r="C24" s="70" t="s">
+      <c r="C24" s="62" t="s">
         <v>150</v>
       </c>
       <c r="D24" s="46" t="s">
@@ -2718,7 +2803,7 @@
       <c r="N24" s="46">
         <v>20</v>
       </c>
-      <c r="O24" s="73" t="s">
+      <c r="O24" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P24" s="55">
@@ -2736,7 +2821,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="72" t="s">
+      <c r="C25" s="64" t="s">
         <v>154</v>
       </c>
       <c r="D25" s="50" t="s">
@@ -2771,7 +2856,7 @@
       <c r="N25" s="50">
         <v>25</v>
       </c>
-      <c r="O25" s="74" t="s">
+      <c r="O25" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P25" s="56">
@@ -2789,7 +2874,7 @@
         <f>ROW(B26) - ROW($B$9)</f>
         <v>17</v>
       </c>
-      <c r="C26" s="70" t="s">
+      <c r="C26" s="62" t="s">
         <v>151</v>
       </c>
       <c r="D26" s="46" t="s">
@@ -2801,10 +2886,10 @@
       <c r="F26" s="46" t="s">
         <v>78</v>
       </c>
-      <c r="G26" s="75">
+      <c r="G26" s="67">
         <v>61300611121</v>
       </c>
-      <c r="H26" s="76" t="s">
+      <c r="H26" s="68" t="s">
         <v>198</v>
       </c>
       <c r="I26" s="46" t="s">
@@ -2826,7 +2911,7 @@
       <c r="N26" s="46">
         <v>40</v>
       </c>
-      <c r="O26" s="73" t="s">
+      <c r="O26" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P26" s="55">
@@ -2835,7 +2920,7 @@
       <c r="Q26" s="55">
         <v>1.26</v>
       </c>
-      <c r="R26" s="77" t="s">
+      <c r="R26" s="69" t="s">
         <v>202</v>
       </c>
       <c r="S26" s="53"/>
@@ -2846,7 +2931,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="C27" s="72" t="s">
+      <c r="C27" s="64" t="s">
         <v>153</v>
       </c>
       <c r="D27" s="50" t="s">
@@ -2881,7 +2966,7 @@
       <c r="N27" s="50">
         <v>20</v>
       </c>
-      <c r="O27" s="74" t="s">
+      <c r="O27" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P27" s="56">
@@ -2899,7 +2984,7 @@
         <f>ROW(B28) - ROW($B$9)</f>
         <v>19</v>
       </c>
-      <c r="C28" s="70" t="s">
+      <c r="C28" s="62" t="s">
         <v>152</v>
       </c>
       <c r="D28" s="46" t="s">
@@ -2934,7 +3019,7 @@
       <c r="N28" s="46">
         <v>12</v>
       </c>
-      <c r="O28" s="73" t="s">
+      <c r="O28" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P28" s="55">
@@ -2952,7 +3037,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="C29" s="72" t="s">
+      <c r="C29" s="64" t="s">
         <v>155</v>
       </c>
       <c r="D29" s="50" t="s">
@@ -2964,7 +3049,7 @@
       <c r="F29" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="G29" s="75" t="s">
+      <c r="G29" s="67" t="s">
         <v>188</v>
       </c>
       <c r="H29" s="50" t="s">
@@ -2989,7 +3074,7 @@
       <c r="N29" s="50">
         <v>100</v>
       </c>
-      <c r="O29" s="74" t="s">
+      <c r="O29" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P29" s="56">
@@ -3007,7 +3092,7 @@
         <f>ROW(B30) - ROW($B$9)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="70" t="s">
+      <c r="C30" s="62" t="s">
         <v>155</v>
       </c>
       <c r="D30" s="46" t="s">
@@ -3042,7 +3127,7 @@
       <c r="N30" s="46">
         <v>100</v>
       </c>
-      <c r="O30" s="73" t="s">
+      <c r="O30" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P30" s="55">
@@ -3060,7 +3145,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="C31" s="72" t="s">
+      <c r="C31" s="64" t="s">
         <v>155</v>
       </c>
       <c r="D31" s="50" t="s">
@@ -3072,7 +3157,7 @@
       <c r="F31" s="50" t="s">
         <v>82</v>
       </c>
-      <c r="G31" s="75" t="s">
+      <c r="G31" s="67" t="s">
         <v>98</v>
       </c>
       <c r="H31" s="50" t="s">
@@ -3097,7 +3182,7 @@
       <c r="N31" s="50">
         <v>100</v>
       </c>
-      <c r="O31" s="74" t="s">
+      <c r="O31" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P31" s="56">
@@ -3115,7 +3200,7 @@
         <f>ROW(B32) - ROW($B$9)</f>
         <v>23</v>
       </c>
-      <c r="C32" s="70" t="s">
+      <c r="C32" s="62" t="s">
         <v>155</v>
       </c>
       <c r="D32" s="46" t="s">
@@ -3150,7 +3235,7 @@
       <c r="N32" s="46">
         <v>100</v>
       </c>
-      <c r="O32" s="73" t="s">
+      <c r="O32" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P32" s="55">
@@ -3168,7 +3253,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="C33" s="72" t="s">
+      <c r="C33" s="64" t="s">
         <v>155</v>
       </c>
       <c r="D33" s="50" t="s">
@@ -3203,7 +3288,7 @@
       <c r="N33" s="50">
         <v>100</v>
       </c>
-      <c r="O33" s="74" t="s">
+      <c r="O33" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P33" s="56">
@@ -3221,7 +3306,7 @@
         <f>ROW(B34) - ROW($B$9)</f>
         <v>25</v>
       </c>
-      <c r="C34" s="70" t="s">
+      <c r="C34" s="62" t="s">
         <v>83</v>
       </c>
       <c r="D34" s="46" t="s">
@@ -3260,7 +3345,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="C35" s="72" t="s">
+      <c r="C35" s="64" t="s">
         <v>156</v>
       </c>
       <c r="D35" s="50" t="s">
@@ -3295,7 +3380,7 @@
       <c r="N35" s="50">
         <v>33</v>
       </c>
-      <c r="O35" s="74" t="s">
+      <c r="O35" s="66" t="s">
         <v>170</v>
       </c>
       <c r="P35" s="56">
@@ -3313,7 +3398,7 @@
         <f>ROW(B36) - ROW($B$9)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="70" t="s">
+      <c r="C36" s="62" t="s">
         <v>157</v>
       </c>
       <c r="D36" s="46" t="s">
@@ -3348,7 +3433,7 @@
       <c r="N36" s="46">
         <v>11</v>
       </c>
-      <c r="O36" s="73" t="s">
+      <c r="O36" s="65" t="s">
         <v>170</v>
       </c>
       <c r="P36" s="55">
@@ -3366,7 +3451,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="C37" s="72" t="s">
+      <c r="C37" s="64" t="s">
         <v>157</v>
       </c>
       <c r="D37" s="50" t="s">
@@ -3381,8 +3466,8 @@
       <c r="G37" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69" t="s">
+      <c r="H37" s="61"/>
+      <c r="I37" s="61" t="s">
         <v>118</v>
       </c>
       <c r="J37" s="52"/>
@@ -3401,13 +3486,13 @@
       </c>
       <c r="O37" s="50"/>
       <c r="P37" s="56"/>
-      <c r="Q37" s="56"/>
-      <c r="R37" s="78" t="s">
+      <c r="Q37" s="84"/>
+      <c r="R37" s="70" t="s">
         <v>203</v>
       </c>
       <c r="S37" s="54"/>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="33"/>
       <c r="C38" s="44"/>
@@ -3421,14 +3506,19 @@
       <c r="K38" s="37"/>
       <c r="L38" s="37"/>
       <c r="M38" s="37"/>
-      <c r="N38" s="37"/>
-      <c r="O38" s="37"/>
-      <c r="P38" s="37"/>
-      <c r="Q38" s="37"/>
-      <c r="R38" s="65"/>
-      <c r="S38" s="66"/>
-    </row>
-    <row r="39" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="N38" s="79" t="s">
+        <v>204</v>
+      </c>
+      <c r="O38" s="80"/>
+      <c r="P38" s="80"/>
+      <c r="Q38" s="85">
+        <f>SUM(Q10:Q37)</f>
+        <v>73.94</v>
+      </c>
+      <c r="R38" s="75"/>
+      <c r="S38" s="76"/>
+    </row>
+    <row r="39" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="25"/>
       <c r="C39" s="45"/>
@@ -3441,16 +3531,54 @@
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="10"/>
-      <c r="O39" s="10"/>
-      <c r="P39" s="10"/>
-      <c r="Q39" s="10"/>
-      <c r="R39" s="67"/>
-      <c r="S39" s="68"/>
+      <c r="M39" s="82"/>
+      <c r="N39" s="79" t="s">
+        <v>205</v>
+      </c>
+      <c r="O39" s="80"/>
+      <c r="P39" s="80"/>
+      <c r="Q39" s="85">
+        <f>Q38/10</f>
+        <v>7.3940000000000001</v>
+      </c>
+      <c r="R39" s="77"/>
+      <c r="S39" s="78"/>
+    </row>
+    <row r="40" spans="1:19" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="M40" s="81"/>
+      <c r="N40" s="83"/>
+      <c r="O40" s="83"/>
+      <c r="P40" s="83"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M41" s="81"/>
+      <c r="N41" s="81"/>
+      <c r="O41" s="81"/>
+      <c r="P41" s="81"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M42" s="81"/>
+      <c r="N42" s="81"/>
+      <c r="O42" s="81"/>
+      <c r="P42" s="81"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M43" s="81"/>
+      <c r="N43" s="81"/>
+      <c r="O43" s="81"/>
+      <c r="P43" s="81"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="M44" s="81"/>
+      <c r="N44" s="81"/>
+      <c r="O44" s="81"/>
+      <c r="P44" s="81"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="N39:P39"/>
+    <mergeCell ref="N40:P40"/>
     <mergeCell ref="K1:S1"/>
     <mergeCell ref="S3:S8"/>
     <mergeCell ref="R38:S39"/>
